--- a/docs/Logic Requirements/Ageipelago Saladin.xlsx
+++ b/docs/Logic Requirements/Ageipelago Saladin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD2FBCA-71C4-4512-BCD3-CF7D87603E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA143C1-24C3-427A-B8CE-CB2D54337513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{AEFAB4D2-F215-45BA-9EF6-82F1BCF340C6}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="203">
   <si>
     <t>The Lion and the Demon</t>
   </si>
@@ -2456,12 +2456,77 @@
   <si>
     <t>Pyramid</t>
   </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Castle Age</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>Feudal - Castle Age</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>No Watch Tower
+No Guard Tower
+No Stone Gate
+No Stone Wall
+No Fortified Gate
+No Fortified Wall
+No Castle</t>
+  </si>
+  <si>
+    <t>No Galley
+No War Galley
+No Petard
+No Mameluke</t>
+  </si>
+  <si>
+    <t>No Medium Warships
+No Fortified Wall
+No Guard Tower
+No Murder Holes
+No Careening
+No Bimaristan</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>No Careening
+No Dry Dock
+No Clinker Construction
+No Carvel Hull
+No Siphons
+No Incendiaries
+No Sappers</t>
+  </si>
+  <si>
+    <t>No Sappers</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2675,6 +2740,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2684,7 +2761,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2820,11 +2897,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2960,6 +3061,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3600,15 +3728,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853A5127-1C52-4219-B26B-767FBE00E695}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -3622,7 +3756,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="37" t="s">
         <v>128</v>
       </c>
@@ -3636,7 +3775,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>192</v>
+      </c>
       <c r="G4" s="14" t="s">
         <v>116</v>
       </c>
@@ -3650,7 +3798,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>193</v>
+      </c>
       <c r="G5" s="14" t="s">
         <v>103</v>
       </c>
@@ -3664,7 +3821,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="10"/>
       <c r="G6" s="39" t="s">
         <v>117</v>
       </c>
@@ -3678,7 +3838,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="10"/>
       <c r="G7" s="14" t="s">
         <v>118</v>
       </c>
@@ -3692,7 +3855,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="10"/>
       <c r="G8" s="14" t="s">
         <v>101</v>
       </c>
@@ -3706,7 +3872,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="10"/>
       <c r="G9" s="13" t="s">
         <v>119</v>
       </c>
@@ -3720,7 +3889,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="10"/>
       <c r="G10" s="13" t="s">
         <v>120</v>
       </c>
@@ -3734,7 +3906,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="10"/>
       <c r="G11" s="42" t="s">
         <v>186</v>
       </c>
@@ -3748,7 +3923,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="10"/>
       <c r="G12" s="13" t="s">
         <v>98</v>
       </c>
@@ -3762,7 +3940,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="10"/>
       <c r="G13" s="20" t="s">
         <v>121</v>
       </c>
@@ -3776,7 +3957,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="10"/>
       <c r="G14" s="21" t="s">
         <v>122</v>
       </c>
@@ -3790,7 +3974,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="10"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="K15" s="13" t="s">
@@ -3800,7 +3987,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="10"/>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
       <c r="K16" s="13" t="s">
@@ -4003,21 +4193,31 @@
       <c r="L42" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{037F023B-37BE-4680-9FAC-E053276B2DC2}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -4031,7 +4231,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="15" t="s">
         <v>111</v>
       </c>
@@ -4045,7 +4250,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>192</v>
+      </c>
       <c r="G4" s="2" t="s">
         <v>109</v>
       </c>
@@ -4059,7 +4273,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>195</v>
+      </c>
       <c r="G5" s="13" t="s">
         <v>119</v>
       </c>
@@ -4073,7 +4296,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="10"/>
       <c r="G6" s="13" t="s">
         <v>103</v>
       </c>
@@ -4087,7 +4313,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="10"/>
       <c r="G7" s="13" t="s">
         <v>118</v>
       </c>
@@ -4101,7 +4330,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="10"/>
       <c r="G8" s="20" t="s">
         <v>105</v>
       </c>
@@ -4115,7 +4347,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="10"/>
       <c r="G9" s="41" t="s">
         <v>129</v>
       </c>
@@ -4129,7 +4364,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="10"/>
       <c r="G10" s="20" t="s">
         <v>76</v>
       </c>
@@ -4143,7 +4381,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="10"/>
       <c r="G11" s="20" t="s">
         <v>101</v>
       </c>
@@ -4157,7 +4398,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="10"/>
       <c r="G12" s="20" t="s">
         <v>89</v>
       </c>
@@ -4171,7 +4415,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="10"/>
       <c r="G13" s="20" t="s">
         <v>130</v>
       </c>
@@ -4185,7 +4432,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="10"/>
       <c r="G14" s="20" t="s">
         <v>131</v>
       </c>
@@ -4199,7 +4449,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="10"/>
       <c r="G15" s="20" t="s">
         <v>132</v>
       </c>
@@ -4213,7 +4466,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="10"/>
       <c r="G16" s="20" t="s">
         <v>122</v>
       </c>
@@ -4464,21 +4720,31 @@
       <c r="L42" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01B2EE5-E16D-45BB-A8B1-B5ACE9400842}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -4492,7 +4758,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="15" t="s">
         <v>109</v>
       </c>
@@ -4506,7 +4777,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>192</v>
+      </c>
       <c r="G4" s="13" t="s">
         <v>105</v>
       </c>
@@ -4520,7 +4800,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>198</v>
+      </c>
       <c r="G5" s="13" t="s">
         <v>119</v>
       </c>
@@ -4534,7 +4823,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="10"/>
       <c r="G6" s="13" t="s">
         <v>95</v>
       </c>
@@ -4548,7 +4840,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="10"/>
       <c r="G7" s="13" t="s">
         <v>103</v>
       </c>
@@ -4562,7 +4857,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="10"/>
       <c r="G8" s="13" t="s">
         <v>143</v>
       </c>
@@ -4576,7 +4874,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="10"/>
       <c r="G9" s="14" t="s">
         <v>144</v>
       </c>
@@ -4590,7 +4891,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="10"/>
       <c r="G10" s="14" t="s">
         <v>132</v>
       </c>
@@ -4604,7 +4908,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="10"/>
       <c r="G11" s="14" t="s">
         <v>101</v>
       </c>
@@ -4618,7 +4925,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="10"/>
       <c r="G12" s="14" t="s">
         <v>130</v>
       </c>
@@ -4632,7 +4942,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="10"/>
       <c r="G13" s="14" t="s">
         <v>118</v>
       </c>
@@ -4646,7 +4959,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="10"/>
       <c r="G14" s="14" t="s">
         <v>121</v>
       </c>
@@ -4660,7 +4976,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="10"/>
       <c r="G15" s="14" t="s">
         <v>145</v>
       </c>
@@ -4674,7 +4993,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="10"/>
       <c r="G16" s="14" t="s">
         <v>133</v>
       </c>
@@ -4857,6 +5179,10 @@
       <c r="L42" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -4864,15 +5190,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400711E2-41E9-4F6A-8D66-AD1A160D8245}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -4886,7 +5218,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="15" t="s">
         <v>111</v>
       </c>
@@ -4900,7 +5237,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>192</v>
+      </c>
       <c r="G4" s="2" t="s">
         <v>109</v>
       </c>
@@ -4914,7 +5260,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="B5" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>200</v>
+      </c>
       <c r="G5" s="26" t="s">
         <v>105</v>
       </c>
@@ -4928,7 +5283,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="10"/>
       <c r="G6" s="26" t="s">
         <v>101</v>
       </c>
@@ -4942,7 +5300,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="10"/>
       <c r="G7" s="26" t="s">
         <v>145</v>
       </c>
@@ -4956,7 +5317,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="10"/>
       <c r="G8" s="26" t="s">
         <v>118</v>
       </c>
@@ -4970,7 +5334,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="10"/>
       <c r="G9" s="26" t="s">
         <v>98</v>
       </c>
@@ -4984,7 +5351,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="10"/>
       <c r="G10" s="26" t="s">
         <v>132</v>
       </c>
@@ -4998,7 +5368,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="10"/>
       <c r="G11" s="26" t="s">
         <v>146</v>
       </c>
@@ -5012,7 +5385,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="10"/>
       <c r="G12" s="26" t="s">
         <v>95</v>
       </c>
@@ -5026,7 +5402,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="10"/>
       <c r="G13" s="44" t="s">
         <v>147</v>
       </c>
@@ -5040,7 +5419,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="10"/>
       <c r="G14" s="27" t="s">
         <v>143</v>
       </c>
@@ -5054,7 +5436,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="10"/>
       <c r="G15" s="14" t="s">
         <v>137</v>
       </c>
@@ -5068,7 +5453,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="10"/>
       <c r="G16" s="14" t="s">
         <v>121</v>
       </c>
@@ -5299,21 +5687,31 @@
       <c r="L42" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6152ECF6-CCB6-4201-9459-562479E56238}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -5327,7 +5725,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="15" t="s">
         <v>111</v>
       </c>
@@ -5341,7 +5744,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>192</v>
+      </c>
       <c r="G4" s="2" t="s">
         <v>109</v>
       </c>
@@ -5355,7 +5767,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>201</v>
+      </c>
       <c r="G5" s="38" t="s">
         <v>157</v>
       </c>
@@ -5369,7 +5790,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="10"/>
       <c r="G6" s="38" t="s">
         <v>158</v>
       </c>
@@ -5383,7 +5807,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="10"/>
       <c r="G7" s="32" t="s">
         <v>118</v>
       </c>
@@ -5397,7 +5824,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="10"/>
       <c r="G8" s="32" t="s">
         <v>103</v>
       </c>
@@ -5411,7 +5841,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="10"/>
       <c r="G9" s="32" t="s">
         <v>132</v>
       </c>
@@ -5425,7 +5858,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="10"/>
       <c r="G10" s="27" t="s">
         <v>105</v>
       </c>
@@ -5439,7 +5875,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="10"/>
       <c r="G11" s="27" t="s">
         <v>122</v>
       </c>
@@ -5453,7 +5892,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="10"/>
       <c r="G12" s="27" t="s">
         <v>130</v>
       </c>
@@ -5467,7 +5909,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="10"/>
       <c r="G13" s="27" t="s">
         <v>78</v>
       </c>
@@ -5481,7 +5926,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="10"/>
       <c r="G14" s="27" t="s">
         <v>159</v>
       </c>
@@ -5495,7 +5943,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="10"/>
       <c r="G15" s="43" t="s">
         <v>160</v>
       </c>
@@ -5509,7 +5960,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="10"/>
       <c r="G16" s="27" t="s">
         <v>161</v>
       </c>
@@ -5766,21 +6220,31 @@
       <c r="L42" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33AE33F0-FC25-41A5-B62E-B291D044B50E}">
-  <dimension ref="G1:L42"/>
+  <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -5794,7 +6258,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
       <c r="G3" s="23" t="s">
         <v>105</v>
       </c>
@@ -5808,7 +6277,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>192</v>
+      </c>
       <c r="G4" s="14" t="s">
         <v>131</v>
       </c>
@@ -5822,7 +6300,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>201</v>
+      </c>
       <c r="G5" s="39" t="s">
         <v>170</v>
       </c>
@@ -5836,7 +6323,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="10"/>
       <c r="G6" s="39" t="s">
         <v>171</v>
       </c>
@@ -5850,7 +6340,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="10"/>
       <c r="G7" s="39" t="s">
         <v>172</v>
       </c>
@@ -5864,7 +6357,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="10"/>
       <c r="G8" s="35" t="s">
         <v>89</v>
       </c>
@@ -5878,7 +6374,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="10"/>
       <c r="G9" s="40" t="s">
         <v>173</v>
       </c>
@@ -5892,7 +6391,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="10"/>
       <c r="G10" s="35" t="s">
         <v>122</v>
       </c>
@@ -5906,7 +6408,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="10"/>
       <c r="G11" s="35" t="s">
         <v>85</v>
       </c>
@@ -5920,7 +6425,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="10"/>
       <c r="G12" s="13" t="s">
         <v>130</v>
       </c>
@@ -5934,7 +6442,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="10"/>
       <c r="G13" s="42" t="s">
         <v>175</v>
       </c>
@@ -5948,7 +6459,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="10"/>
       <c r="G14" s="13" t="s">
         <v>176</v>
       </c>
@@ -5962,7 +6476,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="10"/>
       <c r="G15" s="42" t="s">
         <v>177</v>
       </c>
@@ -5976,7 +6493,10 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="10"/>
       <c r="G16" s="42" t="s">
         <v>178</v>
       </c>
@@ -6211,6 +6731,10 @@
       <c r="L42" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Saladin.xlsx
+++ b/docs/Logic Requirements/Ageipelago Saladin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA143C1-24C3-427A-B8CE-CB2D54337513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320A316E-5A3F-4DD3-BCA9-69DFFA27048B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{AEFAB4D2-F215-45BA-9EF6-82F1BCF340C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{AEFAB4D2-F215-45BA-9EF6-82F1BCF340C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Saladin" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="204">
   <si>
     <t>The Lion and the Demon</t>
   </si>
@@ -2521,12 +2521,36 @@
   <si>
     <t>Imperial Age</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No Sappers
+On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+Guard Tower, Ballistics and Murder Holes are researched automatically</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2748,6 +2772,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -3063,6 +3093,15 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3079,15 +3118,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3738,11 +3768,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -3757,11 +3787,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="53" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="37" t="s">
         <v>128</v>
       </c>
@@ -3799,13 +3829,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="47" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="47" t="s">
         <v>193</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="47" t="s">
         <v>193</v>
       </c>
       <c r="G5" s="14" t="s">
@@ -3822,8 +3852,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="10"/>
       <c r="G6" s="39" t="s">
         <v>117</v>
@@ -3839,8 +3869,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="10"/>
       <c r="G7" s="14" t="s">
         <v>118</v>
@@ -3856,8 +3886,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="10"/>
       <c r="G8" s="14" t="s">
         <v>101</v>
@@ -3873,8 +3903,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="10"/>
       <c r="G9" s="13" t="s">
         <v>119</v>
@@ -3890,8 +3920,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="10"/>
       <c r="G10" s="13" t="s">
         <v>120</v>
@@ -3907,8 +3937,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="10"/>
       <c r="G11" s="42" t="s">
         <v>186</v>
@@ -3924,8 +3954,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="10"/>
       <c r="G12" s="13" t="s">
         <v>98</v>
@@ -3941,8 +3971,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="10"/>
       <c r="G13" s="20" t="s">
         <v>121</v>
@@ -3958,8 +3988,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="10"/>
       <c r="G14" s="21" t="s">
         <v>122</v>
@@ -3975,8 +4005,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="10"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
@@ -3988,8 +4018,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="10"/>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
@@ -4213,11 +4243,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -4232,11 +4262,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="15" t="s">
         <v>111</v>
       </c>
@@ -4274,13 +4304,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="47" t="s">
         <v>195</v>
       </c>
       <c r="G5" s="13" t="s">
@@ -4297,8 +4327,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="10"/>
       <c r="G6" s="13" t="s">
         <v>103</v>
@@ -4314,8 +4344,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="10"/>
       <c r="G7" s="13" t="s">
         <v>118</v>
@@ -4331,8 +4361,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="10"/>
       <c r="G8" s="20" t="s">
         <v>105</v>
@@ -4348,8 +4378,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="10"/>
       <c r="G9" s="41" t="s">
         <v>129</v>
@@ -4365,8 +4395,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="10"/>
       <c r="G10" s="20" t="s">
         <v>76</v>
@@ -4382,8 +4412,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="10"/>
       <c r="G11" s="20" t="s">
         <v>101</v>
@@ -4399,8 +4429,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="10"/>
       <c r="G12" s="20" t="s">
         <v>89</v>
@@ -4416,8 +4446,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="10"/>
       <c r="G13" s="20" t="s">
         <v>130</v>
@@ -4433,8 +4463,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="10"/>
       <c r="G14" s="20" t="s">
         <v>131</v>
@@ -4450,8 +4480,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="10"/>
       <c r="G15" s="20" t="s">
         <v>132</v>
@@ -4467,8 +4497,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="10"/>
       <c r="G16" s="20" t="s">
         <v>122</v>
@@ -4740,11 +4770,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -4759,11 +4789,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="15" t="s">
         <v>109</v>
       </c>
@@ -4801,13 +4831,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="47" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="47" t="s">
         <v>197</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="47" t="s">
         <v>198</v>
       </c>
       <c r="G5" s="13" t="s">
@@ -4824,8 +4854,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="10"/>
       <c r="G6" s="13" t="s">
         <v>95</v>
@@ -4841,8 +4871,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="10"/>
       <c r="G7" s="13" t="s">
         <v>103</v>
@@ -4858,8 +4888,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="10"/>
       <c r="G8" s="13" t="s">
         <v>143</v>
@@ -4875,8 +4905,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="10"/>
       <c r="G9" s="14" t="s">
         <v>144</v>
@@ -4892,8 +4922,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="10"/>
       <c r="G10" s="14" t="s">
         <v>132</v>
@@ -4909,8 +4939,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="10"/>
       <c r="G11" s="14" t="s">
         <v>101</v>
@@ -4926,8 +4956,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="10"/>
       <c r="G12" s="14" t="s">
         <v>130</v>
@@ -4943,8 +4973,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="10"/>
       <c r="G13" s="14" t="s">
         <v>118</v>
@@ -4960,8 +4990,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="10"/>
       <c r="G14" s="14" t="s">
         <v>121</v>
@@ -4977,8 +5007,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="10"/>
       <c r="G15" s="14" t="s">
         <v>145</v>
@@ -4994,8 +5024,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="10"/>
       <c r="G16" s="14" t="s">
         <v>133</v>
@@ -5200,11 +5230,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -5219,11 +5249,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="15" t="s">
         <v>111</v>
       </c>
@@ -5261,13 +5291,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="47" t="s">
         <v>200</v>
       </c>
       <c r="G5" s="26" t="s">
@@ -5284,8 +5314,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="10"/>
       <c r="G6" s="26" t="s">
         <v>101</v>
@@ -5301,8 +5331,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="10"/>
       <c r="G7" s="26" t="s">
         <v>145</v>
@@ -5318,8 +5348,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="10"/>
       <c r="G8" s="26" t="s">
         <v>118</v>
@@ -5335,8 +5365,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="10"/>
       <c r="G9" s="26" t="s">
         <v>98</v>
@@ -5352,8 +5382,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="10"/>
       <c r="G10" s="26" t="s">
         <v>132</v>
@@ -5369,8 +5399,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="10"/>
       <c r="G11" s="26" t="s">
         <v>146</v>
@@ -5386,8 +5416,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="10"/>
       <c r="G12" s="26" t="s">
         <v>95</v>
@@ -5403,8 +5433,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="10"/>
       <c r="G13" s="44" t="s">
         <v>147</v>
@@ -5420,8 +5450,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="10"/>
       <c r="G14" s="27" t="s">
         <v>143</v>
@@ -5437,8 +5467,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="10"/>
       <c r="G15" s="14" t="s">
         <v>137</v>
@@ -5454,8 +5484,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="10"/>
       <c r="G16" s="14" t="s">
         <v>121</v>
@@ -5707,11 +5737,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -5726,11 +5756,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="15" t="s">
         <v>111</v>
       </c>
@@ -5767,15 +5797,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="53" t="s">
+    <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="53" t="s">
-        <v>201</v>
+      <c r="D5" s="47" t="s">
+        <v>203</v>
       </c>
       <c r="G5" s="38" t="s">
         <v>157</v>
@@ -5791,8 +5821,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="10"/>
       <c r="G6" s="38" t="s">
         <v>158</v>
@@ -5808,8 +5838,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="10"/>
       <c r="G7" s="32" t="s">
         <v>118</v>
@@ -5825,8 +5855,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="10"/>
       <c r="G8" s="32" t="s">
         <v>103</v>
@@ -5842,8 +5872,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="10"/>
       <c r="G9" s="32" t="s">
         <v>132</v>
@@ -5859,8 +5889,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="10"/>
       <c r="G10" s="27" t="s">
         <v>105</v>
@@ -5876,8 +5906,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="10"/>
       <c r="G11" s="27" t="s">
         <v>122</v>
@@ -5893,8 +5923,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="10"/>
       <c r="G12" s="27" t="s">
         <v>130</v>
@@ -5910,8 +5940,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="10"/>
       <c r="G13" s="27" t="s">
         <v>78</v>
@@ -5927,8 +5957,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="10"/>
       <c r="G14" s="27" t="s">
         <v>159</v>
@@ -5944,8 +5974,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="10"/>
       <c r="G15" s="43" t="s">
         <v>160</v>
@@ -5961,8 +5991,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="10"/>
       <c r="G16" s="27" t="s">
         <v>161</v>
@@ -6225,6 +6255,7 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6240,11 +6271,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="49"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -6259,11 +6290,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
       <c r="G3" s="23" t="s">
         <v>105</v>
       </c>
@@ -6301,13 +6332,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="47" t="s">
         <v>201</v>
       </c>
       <c r="G5" s="39" t="s">
@@ -6324,8 +6355,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="10"/>
       <c r="G6" s="39" t="s">
         <v>171</v>
@@ -6341,8 +6372,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="10"/>
       <c r="G7" s="39" t="s">
         <v>172</v>
@@ -6358,8 +6389,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="10"/>
       <c r="G8" s="35" t="s">
         <v>89</v>
@@ -6375,8 +6406,8 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="10"/>
       <c r="G9" s="40" t="s">
         <v>173</v>
@@ -6392,8 +6423,8 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="10"/>
       <c r="G10" s="35" t="s">
         <v>122</v>
@@ -6409,8 +6440,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="10"/>
       <c r="G11" s="35" t="s">
         <v>85</v>
@@ -6426,8 +6457,8 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="10"/>
       <c r="G12" s="13" t="s">
         <v>130</v>
@@ -6443,8 +6474,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="10"/>
       <c r="G13" s="42" t="s">
         <v>175</v>
@@ -6460,8 +6491,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="10"/>
       <c r="G14" s="13" t="s">
         <v>176</v>
@@ -6477,8 +6508,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="10"/>
       <c r="G15" s="42" t="s">
         <v>177</v>
@@ -6494,8 +6525,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="10"/>
       <c r="G16" s="42" t="s">
         <v>178</v>

--- a/docs/Logic Requirements/Ageipelago Saladin.xlsx
+++ b/docs/Logic Requirements/Ageipelago Saladin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320A316E-5A3F-4DD3-BCA9-69DFFA27048B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AE1D2B-3C16-4860-A91C-F7CB1C965FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{AEFAB4D2-F215-45BA-9EF6-82F1BCF340C6}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{AEFAB4D2-F215-45BA-9EF6-82F1BCF340C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Saladin" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="215">
   <si>
     <t>The Lion and the Demon</t>
   </si>
@@ -2544,6 +2544,39 @@
       <t>:
 Guard Tower, Ballistics and Murder Holes are researched automatically</t>
     </r>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Heavy Scorpion</t>
+  </si>
+  <si>
+    <t>Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Spearman</t>
+  </si>
+  <si>
+    <t>Mining Camp (Only on Standard)</t>
+  </si>
+  <si>
+    <t>Archer of the Eye</t>
+  </si>
+  <si>
+    <t>Heavy Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Elite War Elephant</t>
   </si>
 </sst>
 </file>
@@ -2955,7 +2988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3099,9 +3132,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3118,6 +3148,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3761,18 +3797,18 @@
   <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -3787,11 +3823,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="37" t="s">
         <v>128</v>
       </c>
@@ -3868,7 +3904,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="10"/>
@@ -3885,10 +3921,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="10"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="G8" s="14" t="s">
         <v>101</v>
       </c>
@@ -3903,9 +3948,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="55"/>
+      <c r="D9" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="55"/>
       <c r="G9" s="13" t="s">
         <v>119</v>
       </c>
@@ -3920,9 +3970,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="E10" s="55"/>
       <c r="G10" s="13" t="s">
         <v>120</v>
       </c>
@@ -3937,9 +3992,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="10"/>
+      <c r="B11" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="55"/>
       <c r="G11" s="42" t="s">
         <v>186</v>
       </c>
@@ -3954,9 +4014,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="10"/>
+      <c r="B12" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="G12" s="13" t="s">
         <v>98</v>
       </c>
@@ -3971,9 +4034,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="10"/>
+      <c r="B13" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
       <c r="G13" s="20" t="s">
         <v>121</v>
       </c>
@@ -3988,9 +4054,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
       <c r="G14" s="21" t="s">
         <v>122</v>
       </c>
@@ -4005,9 +4072,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="K15" s="13" t="s">
@@ -4018,9 +4086,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
       <c r="K16" s="13" t="s">
@@ -4030,7 +4099,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
       <c r="K17" s="13" t="s">
@@ -4040,7 +4113,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
       <c r="K18" s="13" t="s">
@@ -4050,7 +4127,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
       <c r="G19" s="22"/>
       <c r="H19" s="22"/>
       <c r="K19" s="13" t="s">
@@ -4060,7 +4141,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
       <c r="K20" s="13" t="s">
@@ -4070,7 +4155,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
       <c r="K21" s="13" t="s">
@@ -4080,7 +4169,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
       <c r="K22" s="13" t="s">
@@ -4090,7 +4179,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
       <c r="K23" s="42" t="s">
@@ -4100,7 +4189,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="K24" s="20" t="s">
@@ -4110,7 +4199,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="K25" s="21" t="s">
@@ -4120,7 +4209,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
       <c r="K26" s="20" t="s">
@@ -4130,37 +4219,37 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -4237,17 +4326,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -4262,11 +4352,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="15" t="s">
         <v>111</v>
       </c>
@@ -4343,7 +4433,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="10"/>
@@ -4360,10 +4450,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="10"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="G8" s="20" t="s">
         <v>105</v>
       </c>
@@ -4378,9 +4477,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
       <c r="G9" s="41" t="s">
         <v>129</v>
       </c>
@@ -4395,9 +4499,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="20" t="s">
         <v>76</v>
       </c>
@@ -4412,9 +4521,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="10"/>
+      <c r="B11" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="G11" s="20" t="s">
         <v>101</v>
       </c>
@@ -4429,9 +4543,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="10"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="G12" s="20" t="s">
         <v>89</v>
       </c>
@@ -4446,9 +4561,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="10"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
       <c r="G13" s="20" t="s">
         <v>130</v>
       </c>
@@ -4463,9 +4579,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
       <c r="G14" s="20" t="s">
         <v>131</v>
       </c>
@@ -4480,9 +4597,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
       <c r="G15" s="20" t="s">
         <v>132</v>
       </c>
@@ -4497,9 +4615,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
       <c r="G16" s="20" t="s">
         <v>122</v>
       </c>
@@ -4513,7 +4632,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
       <c r="G17" s="20" t="s">
         <v>95</v>
       </c>
@@ -4527,7 +4650,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="G18" s="39" t="s">
         <v>81</v>
       </c>
@@ -4541,7 +4668,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
       <c r="G19" s="39" t="s">
         <v>79</v>
       </c>
@@ -4555,7 +4686,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
       <c r="G20" s="14" t="s">
         <v>78</v>
       </c>
@@ -4569,7 +4704,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
       <c r="G21" s="14" t="s">
         <v>135</v>
       </c>
@@ -4583,7 +4722,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="14" t="s">
         <v>85</v>
       </c>
@@ -4597,7 +4736,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
       <c r="G23" s="14" t="s">
         <v>133</v>
       </c>
@@ -4611,7 +4750,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="25" t="s">
         <v>134</v>
       </c>
@@ -4625,7 +4764,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="25" t="s">
         <v>139</v>
       </c>
@@ -4639,7 +4778,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="27" t="s">
         <v>137</v>
       </c>
@@ -4653,7 +4792,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="43" t="s">
         <v>138</v>
       </c>
@@ -4663,31 +4802,31 @@
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -4764,17 +4903,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -4789,11 +4929,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="15" t="s">
         <v>109</v>
       </c>
@@ -4870,7 +5010,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="10"/>
@@ -4887,10 +5027,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="10"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="G8" s="13" t="s">
         <v>143</v>
       </c>
@@ -4905,9 +5054,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
       <c r="G9" s="14" t="s">
         <v>144</v>
       </c>
@@ -4922,9 +5076,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="14" t="s">
         <v>132</v>
       </c>
@@ -4939,9 +5098,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="10"/>
+      <c r="B11" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="G11" s="14" t="s">
         <v>101</v>
       </c>
@@ -4956,9 +5120,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="10"/>
+      <c r="B12" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="G12" s="14" t="s">
         <v>130</v>
       </c>
@@ -4973,9 +5142,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="10"/>
+      <c r="B13" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
       <c r="G13" s="14" t="s">
         <v>118</v>
       </c>
@@ -4990,9 +5164,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
       <c r="G14" s="14" t="s">
         <v>121</v>
       </c>
@@ -5007,9 +5184,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
       <c r="G15" s="14" t="s">
         <v>145</v>
       </c>
@@ -5024,9 +5204,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="56" t="s">
+        <v>211</v>
+      </c>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
       <c r="G16" s="14" t="s">
         <v>133</v>
       </c>
@@ -5040,7 +5223,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
       <c r="G17" s="26" t="s">
         <v>76</v>
       </c>
@@ -5054,7 +5241,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="G18" s="27" t="s">
         <v>146</v>
       </c>
@@ -5064,7 +5255,11 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
       <c r="G19" s="29" t="s">
         <v>98</v>
       </c>
@@ -5074,79 +5269,87 @@
       <c r="K19" s="22"/>
       <c r="L19" s="22"/>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="K20" s="22"/>
       <c r="L20" s="22"/>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
       <c r="K21" s="22"/>
       <c r="L21" s="22"/>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
       <c r="K22" s="22"/>
       <c r="L22" s="22"/>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -5224,17 +5427,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -5249,11 +5453,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="15" t="s">
         <v>111</v>
       </c>
@@ -5330,7 +5534,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="10"/>
@@ -5347,10 +5551,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="10"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="G8" s="26" t="s">
         <v>118</v>
       </c>
@@ -5365,9 +5578,12 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
       <c r="G9" s="26" t="s">
         <v>98</v>
       </c>
@@ -5382,9 +5598,12 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="26" t="s">
         <v>132</v>
       </c>
@@ -5399,9 +5618,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="10"/>
+      <c r="B11" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="G11" s="26" t="s">
         <v>146</v>
       </c>
@@ -5416,9 +5638,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="10"/>
+      <c r="B12" s="56" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="G12" s="26" t="s">
         <v>95</v>
       </c>
@@ -5433,9 +5658,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="10"/>
+      <c r="B13" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
       <c r="G13" s="44" t="s">
         <v>147</v>
       </c>
@@ -5450,9 +5678,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
       <c r="G14" s="27" t="s">
         <v>143</v>
       </c>
@@ -5467,9 +5696,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
       <c r="G15" s="14" t="s">
         <v>137</v>
       </c>
@@ -5484,9 +5714,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
       <c r="G16" s="14" t="s">
         <v>121</v>
       </c>
@@ -5500,7 +5731,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
       <c r="G17" s="14" t="s">
         <v>148</v>
       </c>
@@ -5514,7 +5749,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="G18" s="14" t="s">
         <v>103</v>
       </c>
@@ -5528,7 +5767,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
       <c r="G19" s="39" t="s">
         <v>149</v>
       </c>
@@ -5542,7 +5785,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
       <c r="G20" s="14" t="s">
         <v>130</v>
       </c>
@@ -5556,7 +5803,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
       <c r="G21" s="14" t="s">
         <v>131</v>
       </c>
@@ -5570,7 +5821,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G22" s="39" t="s">
         <v>150</v>
       </c>
@@ -5584,7 +5835,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G23" s="39" t="s">
         <v>151</v>
       </c>
@@ -5598,7 +5849,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="25" t="s">
         <v>122</v>
       </c>
@@ -5612,49 +5863,49 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="K25" s="31"/>
       <c r="L25" s="31"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
       <c r="K26" s="31"/>
       <c r="L26" s="31"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="K27" s="31"/>
       <c r="L27" s="31"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
       <c r="K28" s="31"/>
       <c r="L28" s="31"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="31"/>
       <c r="L29" s="31"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="31"/>
       <c r="L30" s="31"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="31"/>
       <c r="L31" s="31"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="31"/>
@@ -5730,18 +5981,18 @@
   <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -5756,11 +6007,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="15" t="s">
         <v>111</v>
       </c>
@@ -5837,7 +6088,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="10"/>
@@ -5854,10 +6105,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="10"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="G8" s="32" t="s">
         <v>103</v>
       </c>
@@ -5872,9 +6132,14 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
       <c r="G9" s="32" t="s">
         <v>132</v>
       </c>
@@ -5889,9 +6154,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="27" t="s">
         <v>105</v>
       </c>
@@ -5906,9 +6176,12 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="10"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="G11" s="27" t="s">
         <v>122</v>
       </c>
@@ -5923,9 +6196,12 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="10"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="G12" s="27" t="s">
         <v>130</v>
       </c>
@@ -5940,9 +6216,12 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="10"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
       <c r="G13" s="27" t="s">
         <v>78</v>
       </c>
@@ -5957,9 +6236,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
       <c r="G14" s="27" t="s">
         <v>159</v>
       </c>
@@ -5974,9 +6256,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
       <c r="G15" s="43" t="s">
         <v>160</v>
       </c>
@@ -5991,9 +6276,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
       <c r="G16" s="27" t="s">
         <v>161</v>
       </c>
@@ -6007,7 +6295,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="55"/>
+      <c r="C17" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
       <c r="G17" s="14" t="s">
         <v>120</v>
       </c>
@@ -6021,7 +6315,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="G18" s="39" t="s">
         <v>162</v>
       </c>
@@ -6035,7 +6333,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
       <c r="G19" s="14" t="s">
         <v>118</v>
       </c>
@@ -6049,7 +6351,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
       <c r="G20" s="39" t="s">
         <v>163</v>
       </c>
@@ -6063,7 +6369,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
       <c r="G21" s="14" t="s">
         <v>95</v>
       </c>
@@ -6077,7 +6387,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="14" t="s">
         <v>85</v>
       </c>
@@ -6091,7 +6401,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="14" t="s">
         <v>98</v>
       </c>
@@ -6105,7 +6415,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="26" t="s">
         <v>139</v>
       </c>
@@ -6119,7 +6429,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="26" t="s">
         <v>134</v>
       </c>
@@ -6133,7 +6443,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="26" t="s">
         <v>164</v>
       </c>
@@ -6143,7 +6453,7 @@
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="26" t="s">
         <v>183</v>
       </c>
@@ -6153,7 +6463,7 @@
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="44" t="s">
         <v>165</v>
       </c>
@@ -6163,7 +6473,7 @@
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="45" t="s">
         <v>166</v>
       </c>
@@ -6173,7 +6483,7 @@
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="20" t="s">
         <v>137</v>
       </c>
@@ -6183,11 +6493,11 @@
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
@@ -6265,17 +6575,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
       <c r="G2" s="4" t="s">
         <v>113</v>
       </c>
@@ -6290,11 +6601,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="G3" s="23" t="s">
         <v>105</v>
       </c>
@@ -6371,7 +6682,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="10"/>
@@ -6388,10 +6699,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="10"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="G8" s="35" t="s">
         <v>89</v>
       </c>
@@ -6406,9 +6726,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="55"/>
       <c r="G9" s="40" t="s">
         <v>173</v>
       </c>
@@ -6423,9 +6750,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="35" t="s">
         <v>122</v>
       </c>
@@ -6440,9 +6772,14 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="10"/>
+      <c r="B11" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="G11" s="35" t="s">
         <v>85</v>
       </c>
@@ -6457,9 +6794,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="10"/>
+      <c r="B12" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="G12" s="13" t="s">
         <v>130</v>
       </c>
@@ -6473,10 +6815,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="10"/>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
       <c r="G13" s="42" t="s">
         <v>175</v>
       </c>
@@ -6491,9 +6838,14 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="56" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
       <c r="G14" s="13" t="s">
         <v>176</v>
       </c>
@@ -6508,9 +6860,14 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
       <c r="G15" s="42" t="s">
         <v>177</v>
       </c>
@@ -6525,9 +6882,12 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
       <c r="G16" s="42" t="s">
         <v>178</v>
       </c>
@@ -6541,7 +6901,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="55"/>
+      <c r="C17" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
       <c r="G17" s="44" t="s">
         <v>180</v>
       </c>
@@ -6555,7 +6921,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="55"/>
+      <c r="C18" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="G18" s="44" t="s">
         <v>181</v>
       </c>
@@ -6569,7 +6941,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="55"/>
+      <c r="C19" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
       <c r="G19" s="20" t="s">
         <v>78</v>
       </c>
@@ -6583,7 +6961,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
       <c r="G20" s="20" t="s">
         <v>159</v>
       </c>
@@ -6597,7 +6979,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
       <c r="G21" s="20" t="s">
         <v>183</v>
       </c>
@@ -6611,7 +6997,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G22" s="20" t="s">
         <v>161</v>
       </c>
@@ -6625,7 +7011,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G23" s="41" t="s">
         <v>182</v>
       </c>
@@ -6635,7 +7021,7 @@
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="20" t="s">
         <v>139</v>
       </c>
@@ -6645,7 +7031,7 @@
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="32" t="s">
         <v>145</v>
       </c>
@@ -6655,7 +7041,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="32" t="s">
         <v>148</v>
       </c>
@@ -6665,7 +7051,7 @@
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="36" t="s">
         <v>134</v>
       </c>
@@ -6675,31 +7061,31 @@
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
       <c r="K32" s="22"/>
